--- a/Sample_run/1/student/duongnthe186310/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/duongnthe186310/TC6/GradeDetail.xlsx
@@ -1107,7 +1107,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1166,7 +1166,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1219,7 +1219,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1275,7 +1275,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1334,7 +1334,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1390,7 +1390,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>58</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1558,7 +1558,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1611,7 +1611,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54188</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1723,7 +1723,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1782,7 +1782,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1891,7 +1891,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1950,7 +1950,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -2006,7 +2006,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
         <x:v>58</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2118,7 +2118,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2162,22 +2162,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="Q21" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q21" s="0">
-        <x:v>54288</x:v>
-      </x:c>
-      <x:c r="R21" s="2" t="s">
-        <x:v>48</x:v>
+      <x:c r="R21" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2227,7 +2227,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54288</x:v>
+        <x:v>41712</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2268,28 +2268,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R23" s="4" t="s">
-        <x:v>64</x:v>
+      <x:c r="P23" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q23" s="0">
+        <x:v>41712</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
